--- a/src/test/resources/farmer-import/Template_list_of_farmers_Rwanda_en.xlsx
+++ b/src/test/resources/farmer-import/Template_list_of_farmers_Rwanda_en.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="566">
   <si>
     <t>List of farmers</t>
   </si>
@@ -1723,6 +1723,33 @@
   </si>
   <si>
     <t>8. Geo Data column is in form: POLYGON((lat_1 lon_1, lat_2 lon_2, ...))</t>
+  </si>
+  <si>
+    <t>Geo Data (POLYGON((lat1 lon1, lat2 lon2,...)), POINT(lat lon), GeoJSON, ODK/Kobo geoshape "lat lon alt acc;...", or P1(...)P2(...) for several plots)</t>
+  </si>
+  <si>
+    <t>GeoID (FAO) - identifier of the plot boundary in the FAO GeoID registry</t>
+  </si>
+  <si>
+    <t>8. The Geo Data column accepts any one of these formats - use whichever your GPS, GIS or data collection tool produced, there is no need to convert by hand:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    a) WKT polygon or point, as documented before: POLYGON((lat_1 lon_1, lat_2 lon_2, ...)) or POINT(lat lon). Standard lon/lat WKT from QGIS or PostGIS is also understood.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    b) ODK / KoboToolbox geoshape, geotrace or geopoint, copied straight out of the export: 5.1717367 10.2352433 1267.1 1.45;5.1718067 10.235235 1267.8 1.3;...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    c) GeoJSON: {"type":"Polygon","coordinates":[[[10.235,5.171],[10.236,5.172],[10.237,5.173],[10.235,5.171]]]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    d) Several plots for one farmer: P1(&lt;geo data&gt;)P2(&lt;geo data&gt;), using any of the formats above inside each pair of brackets.</t>
+  </si>
+  <si>
+    <t>9. A farmer with more than one plot can also be spread over several rows: fill the farmer columns once, then put each extra plot on its own row leaving every other column empty.</t>
+  </si>
+  <si>
+    <t>10. The GeoID column takes the identifier of a plot boundary already registered with FAO (https://data.apps.fao.org/geoid). The boundary is fetched from the registry, so no coordinates are needed. If both columns are filled, the GeoID is used and the coordinates serve as a fallback if the registry cannot be reached.</t>
   </si>
 </sst>
 </file>
@@ -3213,7 +3240,7 @@
   <dimension ref="A1:AM260"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="35" max="40" customWidth="true" style="1" width="8.6640625"/>
+    <col min="36" max="40" customWidth="true" style="1" width="8.6640625"/>
     <col min="1" max="1" customWidth="true" style="1" width="25.33203125"/>
     <col min="2" max="2" customWidth="true" style="1" width="17.0"/>
     <col min="3" max="3" customWidth="true" style="1" width="26.1640625"/>
@@ -3244,6 +3271,7 @@
     <col min="32" max="32" customWidth="true" style="1" width="25.5"/>
     <col min="33" max="33" customWidth="true" style="1" width="22.6640625"/>
     <col min="34" max="34" customWidth="true" style="1" width="29.5703125"/>
+    <col min="35" max="35" customWidth="true" style="1" width="29.5703125"/>
     <col min="41" max="16384" style="1" width="8.6640625"/>
   </cols>
   <sheetData>
@@ -3514,9 +3542,11 @@
         <v>27</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>555</v>
-      </c>
-      <c r="AI5" s="3"/>
+        <v>557</v>
+      </c>
+      <c r="AI5" s="11" t="s">
+        <v>558</v>
+      </c>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
@@ -13991,7 +14021,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35E3FE89-249F-674E-9B90-F7679437A92E}">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="25" width="161.83203125"/>
@@ -14040,7 +14070,37 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="25">
-        <v>556</v>
+        <v>559</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
